--- a/xlsx/Tchaikovsky.xlsx
+++ b/xlsx/Tchaikovsky.xlsx
@@ -488,7 +488,7 @@
     <t>ČW 25</t>
   </si>
   <si>
-    <t>Manfred</t>
+    <t>Symphony "Manfred"</t>
   </si>
   <si>
     <t>B minor</t>
@@ -5617,7 +5617,6 @@
       <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1"/>
       <c r="E3" s="1">
         <v>1869</v>
       </c>
@@ -5641,7 +5640,6 @@
       <c r="C4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
@@ -5677,8 +5675,6 @@
       <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="3"/>
       <c r="J5" s="5" t="s">
         <v>28</v>
       </c>
@@ -5722,7 +5718,6 @@
       <c r="C7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
         <v>37</v>
       </c>
@@ -5749,7 +5744,6 @@
       <c r="C8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
         <v>43</v>
       </c>
@@ -5776,7 +5770,6 @@
       <c r="C9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="1"/>
       <c r="E9" s="1">
         <v>1885</v>
       </c>
@@ -5800,7 +5793,6 @@
       <c r="C10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
         <v>53</v>
       </c>
@@ -5810,7 +5802,6 @@
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="1"/>
       <c r="J10" s="5" t="s">
         <v>55</v>
       </c>
@@ -5921,7 +5912,6 @@
       <c r="G14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="1"/>
       <c r="I14" s="3" t="s">
         <v>76</v>
       </c>
@@ -5951,7 +5941,6 @@
       <c r="G15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="1"/>
       <c r="I15" s="3" t="s">
         <v>82</v>
       </c>
@@ -5969,7 +5958,6 @@
       <c r="C16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
         <v>86</v>
       </c>
@@ -5993,7 +5981,6 @@
       <c r="C17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
         <v>92</v>
       </c>
@@ -6003,7 +5990,6 @@
       <c r="G17" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="1"/>
       <c r="J17" s="4" t="s">
         <v>94</v>
       </c>
@@ -6018,7 +6004,6 @@
       <c r="C18" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="1"/>
       <c r="E18" s="1">
         <v>1867</v>
       </c>
@@ -6028,7 +6013,6 @@
       <c r="G18" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H18" s="1"/>
       <c r="J18" s="4" t="s">
         <v>98</v>
       </c>
@@ -6043,7 +6027,6 @@
       <c r="C19" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="1"/>
       <c r="E19" s="1">
         <v>1872</v>
       </c>
@@ -6053,7 +6036,6 @@
       <c r="G19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="1"/>
       <c r="J19" s="4" t="s">
         <v>102</v>
       </c>
@@ -6094,7 +6076,6 @@
       <c r="C21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
         <v>109</v>
       </c>
@@ -6118,7 +6099,6 @@
       <c r="C22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="1"/>
       <c r="E22" s="1">
         <v>1880</v>
       </c>
@@ -6142,7 +6122,6 @@
       <c r="C23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="1"/>
       <c r="E23" s="1">
         <v>1886</v>
       </c>
@@ -6649,7 +6628,6 @@
       <c r="F41" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G41" s="1"/>
       <c r="H41" s="1" t="s">
         <v>139</v>
       </c>
@@ -6673,7 +6651,6 @@
       <c r="F42" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
         <v>135</v>
       </c>
@@ -6726,7 +6703,6 @@
       <c r="F44" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G44" s="1"/>
       <c r="H44" s="1" t="s">
         <v>217</v>
       </c>
@@ -6750,7 +6726,6 @@
       <c r="F45" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
         <v>144</v>
       </c>
@@ -6780,7 +6755,6 @@
       <c r="F46" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
         <v>225</v>
       </c>
@@ -6807,7 +6781,6 @@
       <c r="F47" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G47" s="1"/>
       <c r="H47" s="1" t="s">
         <v>154</v>
       </c>
@@ -6837,7 +6810,6 @@
       <c r="F48" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
         <v>217</v>
       </c>
@@ -6867,7 +6839,6 @@
       <c r="F49" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
         <v>169</v>
       </c>
@@ -6920,7 +6891,6 @@
       <c r="F51" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
         <v>139</v>
       </c>
@@ -6935,14 +6905,12 @@
       <c r="C52" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D52" s="1"/>
       <c r="E52" s="1">
         <v>1884</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G52" s="1"/>
       <c r="H52" s="1" t="s">
         <v>175</v>
       </c>
@@ -6966,7 +6934,6 @@
       <c r="F53" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="G53" s="1"/>
       <c r="H53" s="1" t="s">
         <v>139</v>
       </c>
@@ -7022,7 +6989,6 @@
       <c r="F55" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
         <v>262</v>
       </c>
@@ -7078,7 +7044,6 @@
       <c r="F57" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="G57" s="1"/>
       <c r="H57" s="1" t="s">
         <v>225</v>
       </c>
@@ -7108,7 +7073,6 @@
       <c r="F58" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="G58" s="1"/>
       <c r="H58" s="1" t="s">
         <v>217</v>
       </c>
@@ -7138,7 +7102,6 @@
       <c r="F59" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="G59" s="1"/>
       <c r="H59" s="1" t="s">
         <v>169</v>
       </c>
@@ -7165,7 +7128,6 @@
       <c r="F60" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
         <v>139</v>
       </c>
@@ -7224,7 +7186,6 @@
       <c r="F62" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
         <v>175</v>
       </c>
@@ -7254,7 +7215,6 @@
       <c r="F63" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
         <v>149</v>
       </c>
@@ -7281,7 +7241,6 @@
       <c r="F64" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
         <v>304</v>
       </c>
@@ -7308,7 +7267,6 @@
       <c r="F65" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
         <v>164</v>
       </c>
@@ -7361,7 +7319,6 @@
       <c r="F67" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
         <v>316</v>
       </c>
@@ -7411,7 +7368,6 @@
       <c r="F69" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G69" s="1"/>
       <c r="H69" s="1" t="s">
         <v>217</v>
       </c>
@@ -7464,7 +7420,6 @@
       <c r="F71" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="G71" s="1"/>
       <c r="H71" s="1" t="s">
         <v>135</v>
       </c>
@@ -7488,7 +7443,6 @@
       <c r="F72" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G72" s="1"/>
       <c r="H72" s="1" t="s">
         <v>139</v>
       </c>
@@ -7512,7 +7466,6 @@
       <c r="F73" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="G73" s="1"/>
       <c r="H73" s="1" t="s">
         <v>347</v>
       </c>
@@ -7536,7 +7489,6 @@
       <c r="F74" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="G74" s="1"/>
       <c r="H74" s="1" t="s">
         <v>169</v>
       </c>
@@ -7560,7 +7512,6 @@
       <c r="F75" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="G75" s="1"/>
       <c r="H75" s="1" t="s">
         <v>175</v>
       </c>
@@ -7587,8 +7538,6 @@
       <c r="F76" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
       <c r="J76" s="4" t="s">
         <v>361</v>
       </c>
@@ -7609,7 +7558,6 @@
       <c r="F77" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="G77" s="1"/>
       <c r="J77" s="4" t="s">
         <v>353</v>
       </c>
@@ -7633,8 +7581,6 @@
       <c r="F78" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
       <c r="J78" s="4" t="s">
         <v>369</v>
       </c>
@@ -7655,8 +7601,6 @@
       <c r="F79" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
       <c r="J79" s="4" t="s">
         <v>374</v>
       </c>
@@ -7677,7 +7621,6 @@
       <c r="F80" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="G80" s="1"/>
       <c r="H80" s="1" t="s">
         <v>201</v>
       </c>
@@ -7701,7 +7644,6 @@
       <c r="F81" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="G81" s="1"/>
       <c r="H81" s="1" t="s">
         <v>381</v>
       </c>
@@ -7719,14 +7661,12 @@
       <c r="C82" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D82" s="1"/>
       <c r="E82" s="1">
         <v>1887</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
         <v>175</v>
       </c>
@@ -7744,18 +7684,15 @@
       <c r="C83" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D83" s="1"/>
       <c r="E83" s="1">
         <v>1887</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="G83" s="1"/>
       <c r="H83" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I83" s="3"/>
       <c r="J83" s="4" t="s">
         <v>389</v>
       </c>
@@ -7770,18 +7707,15 @@
       <c r="C84" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D84" s="1"/>
       <c r="E84" s="1">
         <v>1887</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I84" s="3"/>
       <c r="J84" s="4" t="s">
         <v>393</v>
       </c>
@@ -7796,18 +7730,15 @@
       <c r="C85" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D85" s="1"/>
       <c r="E85" s="1">
         <v>1889</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I85" s="3"/>
       <c r="J85" s="4" t="s">
         <v>389</v>
       </c>
@@ -7831,11 +7762,9 @@
       <c r="F86" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="G86" s="1"/>
       <c r="H86" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I86" s="3"/>
       <c r="J86" s="4" t="s">
         <v>401</v>
       </c>
@@ -7850,18 +7779,15 @@
       <c r="C87" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D87" s="1"/>
       <c r="E87" s="1">
         <v>1889</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="G87" s="1"/>
       <c r="H87" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="I87" s="3"/>
       <c r="J87" s="4" t="s">
         <v>405</v>
       </c>
@@ -7876,16 +7802,12 @@
       <c r="C88" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D88" s="1"/>
       <c r="E88" s="1">
         <v>1891</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="3"/>
       <c r="J88" s="4" t="s">
         <v>357</v>
       </c>
@@ -7912,7 +7834,6 @@
       <c r="H89" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="I89" s="3"/>
       <c r="J89" s="4" t="s">
         <v>413</v>
       </c>
@@ -7953,7 +7874,6 @@
       <c r="C91" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
         <v>422</v>
       </c>
@@ -7966,7 +7886,6 @@
       <c r="H91" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I91" s="3"/>
       <c r="J91" s="4" t="s">
         <v>419</v>
       </c>
@@ -8016,7 +7935,6 @@
       <c r="G93" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="H93" s="1"/>
       <c r="J93" s="4" t="s">
         <v>419</v>
       </c>
@@ -8040,8 +7958,6 @@
       <c r="F94" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
       <c r="J94" s="4" t="s">
         <v>435</v>
       </c>
@@ -8056,7 +7972,6 @@
       <c r="C95" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D95" s="1"/>
       <c r="E95" s="1" t="s">
         <v>438</v>
       </c>
@@ -8069,7 +7984,6 @@
       <c r="H95" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I95" s="3"/>
       <c r="J95" s="4" t="s">
         <v>419</v>
       </c>
@@ -8107,16 +8021,12 @@
       <c r="C97" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D97" s="1"/>
       <c r="E97" s="1">
         <v>1873</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="3"/>
       <c r="J97" s="4" t="s">
         <v>435</v>
       </c>
@@ -8140,9 +8050,6 @@
       <c r="F98" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="3"/>
       <c r="J98" s="4" t="s">
         <v>435</v>
       </c>
@@ -8166,9 +8073,6 @@
       <c r="F99" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="3"/>
       <c r="J99" s="4" t="s">
         <v>435</v>
       </c>
@@ -8206,7 +8110,6 @@
       <c r="C101" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="D101" s="1"/>
       <c r="E101" s="1">
         <v>1875</v>
       </c>
@@ -8351,8 +8254,6 @@
       <c r="F107" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
       <c r="J107" s="4" t="s">
         <v>435</v>
       </c>
@@ -8376,9 +8277,6 @@
       <c r="F108" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="3"/>
       <c r="J108" s="4" t="s">
         <v>435</v>
       </c>
@@ -8402,8 +8300,6 @@
       <c r="F109" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
       <c r="J109" s="4" t="s">
         <v>435</v>
       </c>
@@ -8441,7 +8337,6 @@
       <c r="C111" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D111" s="1"/>
       <c r="E111" s="1">
         <v>1865</v>
       </c>
@@ -8454,7 +8349,6 @@
       <c r="H111" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="I111" s="3"/>
       <c r="J111" s="4" t="s">
         <v>481</v>
       </c>
@@ -8585,7 +8479,6 @@
       <c r="H116" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I116" s="3"/>
       <c r="J116" s="4" t="s">
         <v>496</v>
       </c>
@@ -8609,8 +8502,6 @@
       <c r="F117" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
       <c r="J117" s="4" t="s">
         <v>503</v>
       </c>
@@ -8680,7 +8571,6 @@
       <c r="C120" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="D120" s="1"/>
       <c r="E120" s="1">
         <v>1854</v>
       </c>
@@ -8727,7 +8617,6 @@
       <c r="F122" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
         <v>262</v>
       </c>
@@ -8912,7 +8801,6 @@
       <c r="F130" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="G130" s="1"/>
       <c r="H130" s="1" t="s">
         <v>217</v>
       </c>
@@ -8936,7 +8824,6 @@
       <c r="F131" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="G131" s="1"/>
       <c r="H131" s="1" t="s">
         <v>347</v>
       </c>
@@ -9000,8 +8887,6 @@
       <c r="F134" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="G134" s="1"/>
-      <c r="H134" s="1"/>
       <c r="I134" s="3" t="s">
         <v>566</v>
       </c>
@@ -9088,8 +8973,6 @@
       <c r="F138" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="G138" s="1"/>
-      <c r="H138" s="1"/>
       <c r="J138" s="4" t="s">
         <v>582</v>
       </c>
@@ -9127,7 +9010,6 @@
       <c r="C140" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="D140" s="1"/>
       <c r="E140" s="1">
         <v>1878</v>
       </c>
@@ -9177,7 +9059,6 @@
       <c r="F142" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
         <v>175</v>
       </c>
@@ -9218,7 +9099,6 @@
       <c r="F144" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
         <v>175</v>
       </c>
@@ -9242,7 +9122,6 @@
       <c r="F145" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
         <v>135</v>
       </c>
@@ -9266,7 +9145,6 @@
       <c r="F146" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="G146" s="1"/>
       <c r="H146" s="1" t="s">
         <v>217</v>
       </c>
@@ -9287,7 +9165,6 @@
       <c r="F147" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
         <v>609</v>
       </c>
@@ -9302,14 +9179,12 @@
       <c r="C148" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
         <v>612</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
         <v>154</v>
       </c>
@@ -9330,7 +9205,6 @@
       <c r="F149" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
         <v>609</v>
       </c>
@@ -9345,14 +9219,12 @@
       <c r="C150" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="D150" s="1"/>
       <c r="E150" s="1">
         <v>1893</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="G150" s="1"/>
       <c r="H150" s="1" t="s">
         <v>381</v>
       </c>
@@ -9387,7 +9259,6 @@
       <c r="C152" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="D152" s="1"/>
       <c r="E152" s="1" t="s">
         <v>625</v>
       </c>
@@ -9397,7 +9268,6 @@
       <c r="H152" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I152" s="3"/>
       <c r="J152" s="4" t="s">
         <v>627</v>
       </c>
@@ -9412,14 +9282,12 @@
       <c r="C153" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="D153" s="1"/>
       <c r="E153" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="G153" s="1"/>
       <c r="H153" s="1" t="s">
         <v>631</v>
       </c>
@@ -9437,18 +9305,15 @@
       <c r="C154" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="D154" s="1"/>
       <c r="E154" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="G154" s="1"/>
       <c r="H154" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="I154" s="3"/>
       <c r="J154" s="4" t="s">
         <v>632</v>
       </c>
@@ -9463,18 +9328,15 @@
       <c r="C155" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="D155" s="1"/>
       <c r="E155" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="G155" s="1"/>
       <c r="H155" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I155" s="3"/>
       <c r="J155" s="4" t="s">
         <v>632</v>
       </c>
@@ -9489,14 +9351,12 @@
       <c r="C156" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="D156" s="1"/>
       <c r="E156" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="G156" s="1"/>
       <c r="H156" s="1" t="s">
         <v>169</v>
       </c>
@@ -9514,7 +9374,6 @@
       <c r="C157" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D157" s="1"/>
       <c r="E157" s="1" t="s">
         <v>625</v>
       </c>
@@ -9538,18 +9397,15 @@
       <c r="C158" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="D158" s="1"/>
       <c r="E158" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="G158" s="1"/>
       <c r="H158" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="I158" s="3"/>
       <c r="J158" s="4" t="s">
         <v>650</v>
       </c>
@@ -9564,14 +9420,12 @@
       <c r="C159" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="D159" s="1"/>
       <c r="E159" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="G159" s="1"/>
       <c r="H159" s="1" t="s">
         <v>135</v>
       </c>
@@ -9589,14 +9443,12 @@
       <c r="C160" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="D160" s="1"/>
       <c r="E160" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="G160" s="1"/>
       <c r="H160" s="1" t="s">
         <v>201</v>
       </c>
@@ -9614,14 +9466,12 @@
       <c r="C161" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="D161" s="1"/>
       <c r="E161" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="G161" s="1"/>
       <c r="H161" s="1" t="s">
         <v>175</v>
       </c>
@@ -9639,14 +9489,12 @@
       <c r="C162" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="D162" s="1"/>
       <c r="E162" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="G162" s="1"/>
       <c r="H162" s="1" t="s">
         <v>139</v>
       </c>
@@ -9664,14 +9512,12 @@
       <c r="C163" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="D163" s="1"/>
       <c r="E163" s="1" t="s">
         <v>625</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="G163" s="1"/>
       <c r="H163" s="1" t="s">
         <v>154</v>
       </c>
@@ -9689,7 +9535,6 @@
       <c r="C164" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="D164" s="1"/>
       <c r="E164" s="1" t="s">
         <v>625</v>
       </c>
@@ -9736,7 +9581,6 @@
       <c r="C166" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="D166" s="1"/>
       <c r="E166" s="1" t="s">
         <v>677</v>
       </c>
@@ -9757,15 +9601,12 @@
       <c r="C167" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="D167" s="1"/>
       <c r="E167" s="1" t="s">
         <v>682</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="G167" s="1"/>
-      <c r="H167" s="1"/>
       <c r="J167" s="4" t="s">
         <v>684</v>
       </c>
@@ -9780,7 +9621,6 @@
       <c r="C168" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="D168" s="1"/>
       <c r="E168" s="1" t="s">
         <v>522</v>
       </c>
@@ -9801,7 +9641,6 @@
       <c r="C169" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="D169" s="1"/>
       <c r="E169" s="1" t="s">
         <v>522</v>
       </c>
@@ -9822,15 +9661,12 @@
       <c r="C170" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="D170" s="1"/>
       <c r="E170" s="1" t="s">
         <v>695</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="G170" s="1"/>
-      <c r="H170" s="1"/>
       <c r="J170" s="4" t="s">
         <v>697</v>
       </c>
@@ -9845,7 +9681,6 @@
       <c r="C171" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="D171" s="1"/>
       <c r="E171" s="1" t="s">
         <v>700</v>
       </c>
@@ -9866,15 +9701,12 @@
       <c r="C172" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="D172" s="1"/>
       <c r="E172" s="1" t="s">
         <v>705</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="G172" s="1"/>
-      <c r="H172" s="1"/>
       <c r="J172" s="4" t="s">
         <v>707</v>
       </c>
@@ -9889,16 +9721,12 @@
       <c r="C173" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="D173" s="1"/>
       <c r="E173" s="1">
         <v>1867</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="G173" s="1"/>
-      <c r="H173" s="1"/>
-      <c r="I173" s="3"/>
       <c r="J173" s="4" t="s">
         <v>711</v>
       </c>
@@ -9919,8 +9747,6 @@
       <c r="F174" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="G174" s="1"/>
-      <c r="H174" s="1"/>
       <c r="J174" s="4" t="s">
         <v>715</v>
       </c>
@@ -9941,8 +9767,6 @@
       <c r="F175" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="G175" s="1"/>
-      <c r="H175" s="1"/>
       <c r="J175" s="4" t="s">
         <v>719</v>
       </c>
@@ -9963,8 +9787,6 @@
       <c r="F176" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="G176" s="1"/>
-      <c r="H176" s="1"/>
       <c r="J176" s="4" t="s">
         <v>724</v>
       </c>
@@ -9979,15 +9801,12 @@
       <c r="C177" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="D177" s="1"/>
       <c r="E177" s="1">
         <v>1869</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="G177" s="1"/>
-      <c r="H177" s="1"/>
       <c r="J177" s="4" t="s">
         <v>728</v>
       </c>
@@ -10002,15 +9821,12 @@
       <c r="C178" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="D178" s="1"/>
       <c r="E178" s="1">
         <v>1870</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="G178" s="1"/>
-      <c r="H178" s="1"/>
       <c r="J178" s="4" t="s">
         <v>732</v>
       </c>
@@ -10025,15 +9841,12 @@
       <c r="C179" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D179" s="1"/>
       <c r="E179" s="1" t="s">
         <v>438</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="G179" s="1"/>
-      <c r="H179" s="1"/>
       <c r="J179" s="4" t="s">
         <v>736</v>
       </c>
@@ -10048,14 +9861,12 @@
       <c r="C180" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="D180" s="1"/>
       <c r="E180" s="1">
         <v>1871</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="G180" s="1"/>
       <c r="J180" s="4" t="s">
         <v>740</v>
       </c>
@@ -10070,16 +9881,12 @@
       <c r="C181" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="D181" s="1"/>
       <c r="E181" s="1" t="s">
         <v>351</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="G181" s="1"/>
-      <c r="H181" s="1"/>
-      <c r="I181" s="3"/>
       <c r="J181" s="4" t="s">
         <v>744</v>
       </c>
@@ -10094,16 +9901,12 @@
       <c r="C182" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="D182" s="1"/>
       <c r="E182" s="1" t="s">
         <v>747</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="G182" s="1"/>
-      <c r="H182" s="1"/>
-      <c r="I182" s="3"/>
       <c r="J182" s="4" t="s">
         <v>749</v>
       </c>
@@ -10124,7 +9927,6 @@
       <c r="F183" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="G183" s="1"/>
       <c r="J183" s="4" t="s">
         <v>753</v>
       </c>
@@ -10139,16 +9941,12 @@
       <c r="C184" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="D184" s="1"/>
       <c r="E184" s="1">
         <v>1874</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="G184" s="1"/>
-      <c r="H184" s="1"/>
-      <c r="I184" s="3"/>
       <c r="J184" s="4" t="s">
         <v>757</v>
       </c>
@@ -10163,16 +9961,12 @@
       <c r="C185" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="D185" s="1"/>
       <c r="E185" s="1">
         <v>1874</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="G185" s="1"/>
-      <c r="H185" s="1"/>
-      <c r="I185" s="3"/>
       <c r="J185" s="4" t="s">
         <v>761</v>
       </c>
@@ -10187,7 +9981,6 @@
       <c r="C186" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="D186" s="1"/>
       <c r="E186" s="1">
         <v>1874</v>
       </c>
@@ -10208,7 +10001,6 @@
       <c r="C187" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="D187" s="1"/>
       <c r="E187" s="1">
         <v>1874</v>
       </c>
@@ -10218,7 +10010,6 @@
       <c r="G187" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="H187" s="1"/>
       <c r="J187" s="4" t="s">
         <v>769</v>
       </c>
@@ -10233,7 +10024,6 @@
       <c r="C188" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="D188" s="1"/>
       <c r="E188" s="1">
         <v>1876</v>
       </c>
@@ -10243,8 +10033,6 @@
       <c r="G188" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H188" s="1"/>
-      <c r="I188" s="3"/>
       <c r="J188" s="4" t="s">
         <v>773</v>
       </c>
@@ -10259,16 +10047,12 @@
       <c r="C189" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="D189" s="1"/>
       <c r="E189" s="1" t="s">
         <v>776</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="G189" s="1"/>
-      <c r="H189" s="1"/>
-      <c r="I189" s="3"/>
       <c r="J189" s="4" t="s">
         <v>777</v>
       </c>
@@ -10283,16 +10067,12 @@
       <c r="C190" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="D190" s="1"/>
       <c r="E190" s="1">
         <v>1881</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="G190" s="1"/>
-      <c r="H190" s="1"/>
-      <c r="I190" s="3"/>
       <c r="J190" s="4" t="s">
         <v>781</v>
       </c>
@@ -10327,7 +10107,6 @@
       <c r="C192" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="D192" s="1"/>
       <c r="E192" s="1">
         <v>1888</v>
       </c>
@@ -10348,15 +10127,12 @@
       <c r="C193" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="D193" s="1"/>
       <c r="E193" s="1">
         <v>1892</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="G193" s="1"/>
-      <c r="H193" s="1"/>
       <c r="J193" s="4" t="s">
         <v>793</v>
       </c>
@@ -10377,8 +10153,6 @@
       <c r="F194" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="G194" s="1"/>
-      <c r="H194" s="1"/>
       <c r="J194" s="4" t="s">
         <v>797</v>
       </c>
@@ -10393,18 +10167,15 @@
       <c r="C195" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="D195" s="1"/>
       <c r="E195" s="1">
         <v>1876</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="G195" s="1"/>
       <c r="H195" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I195" s="3"/>
       <c r="J195" s="4" t="s">
         <v>801</v>
       </c>
@@ -10425,7 +10196,6 @@
       <c r="F196" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="G196" s="1"/>
       <c r="H196" s="1" t="s">
         <v>169</v>
       </c>
@@ -10443,14 +10213,12 @@
       <c r="C197" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="D197" s="1"/>
       <c r="E197" s="1">
         <v>1882</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="G197" s="1"/>
       <c r="J197" s="4" t="s">
         <v>809</v>
       </c>
@@ -10471,7 +10239,6 @@
       <c r="F198" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="G198" s="1"/>
       <c r="H198" s="1" t="s">
         <v>262</v>
       </c>
@@ -10486,15 +10253,12 @@
       <c r="B199" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
       <c r="E199" s="1">
         <v>1893</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="G199" s="1"/>
       <c r="H199" s="1" t="s">
         <v>169</v>
       </c>
@@ -10518,7 +10282,6 @@
       <c r="F200" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="G200" s="1"/>
       <c r="H200" s="1" t="s">
         <v>201</v>
       </c>
@@ -10545,7 +10308,6 @@
       <c r="G201" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H201" s="1"/>
       <c r="J201" s="4" t="s">
         <v>822</v>
       </c>
@@ -10557,14 +10319,12 @@
       <c r="B202" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="C202" s="1"/>
       <c r="E202" s="1" t="s">
         <v>824</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="G202" s="1"/>
       <c r="H202" s="1" t="s">
         <v>175</v>
       </c>
@@ -10588,7 +10348,6 @@
       <c r="F203" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="G203" s="1"/>
       <c r="H203" s="1" t="s">
         <v>144</v>
       </c>
@@ -10615,7 +10374,6 @@
       <c r="G204" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H204" s="1"/>
       <c r="J204" s="4" t="s">
         <v>832</v>
       </c>
@@ -10630,15 +10388,12 @@
       <c r="C205" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="D205" s="1"/>
       <c r="E205" s="1" t="s">
         <v>835</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="G205" s="1"/>
-      <c r="H205" s="1"/>
       <c r="J205" s="4" t="s">
         <v>837</v>
       </c>
@@ -10662,7 +10417,6 @@
       <c r="G206" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H206" s="1"/>
       <c r="J206" s="4" t="s">
         <v>832</v>
       </c>
@@ -10686,7 +10440,6 @@
       <c r="G207" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H207" s="1"/>
       <c r="J207" s="4" t="s">
         <v>844</v>
       </c>
@@ -10701,7 +10454,6 @@
       <c r="C208" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="D208" s="1"/>
       <c r="E208" s="1">
         <v>1870</v>
       </c>
@@ -10711,7 +10463,6 @@
       <c r="G208" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H208" s="1"/>
       <c r="J208" s="4" t="s">
         <v>832</v>
       </c>
@@ -10735,7 +10486,6 @@
       <c r="G209" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H209" s="1"/>
       <c r="J209" s="4" t="s">
         <v>851</v>
       </c>
@@ -10785,7 +10535,6 @@
       <c r="G211" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H211" s="1"/>
       <c r="J211" s="4" t="s">
         <v>858</v>
       </c>
@@ -10809,7 +10558,6 @@
       <c r="G212" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H212" s="1"/>
       <c r="J212" s="4" t="s">
         <v>832</v>
       </c>
@@ -10833,7 +10581,6 @@
       <c r="G213" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H213" s="1"/>
       <c r="J213" s="4" t="s">
         <v>858</v>
       </c>
@@ -10857,7 +10604,6 @@
       <c r="G214" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H214" s="1"/>
       <c r="J214" s="4" t="s">
         <v>832</v>
       </c>
@@ -10878,8 +10624,6 @@
       <c r="F215" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G215" s="1"/>
-      <c r="H215" s="1"/>
       <c r="J215" s="4" t="s">
         <v>837</v>
       </c>
@@ -10903,7 +10647,6 @@
       <c r="G216" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H216" s="1"/>
       <c r="J216" s="4" t="s">
         <v>832</v>
       </c>
@@ -10915,15 +10658,12 @@
       <c r="B217" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="C217" s="1"/>
       <c r="E217" s="1" t="s">
         <v>875</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="G217" s="1"/>
-      <c r="H217" s="1"/>
       <c r="J217" s="4" t="s">
         <v>825</v>
       </c>
@@ -10938,7 +10678,6 @@
       <c r="C218" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="D218" s="1"/>
       <c r="E218" s="1" t="s">
         <v>879</v>
       </c>
@@ -10948,7 +10687,6 @@
       <c r="G218" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H218" s="1"/>
       <c r="J218" s="4" t="s">
         <v>832</v>
       </c>
@@ -10960,7 +10698,6 @@
       <c r="B219" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="C219" s="1"/>
       <c r="D219" s="1" t="s">
         <v>882</v>
       </c>
@@ -10973,7 +10710,6 @@
       <c r="G219" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H219" s="1"/>
       <c r="J219" s="4" t="s">
         <v>883</v>
       </c>
@@ -10985,14 +10721,12 @@
       <c r="B220" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="C220" s="1"/>
       <c r="E220" s="1">
         <v>1883</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="G220" s="1"/>
       <c r="J220" s="4" t="s">
         <v>825</v>
       </c>
@@ -11024,16 +10758,12 @@
       <c r="B222" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
       <c r="E222" s="1" t="s">
         <v>891</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="G222" s="1"/>
-      <c r="H222" s="1"/>
       <c r="J222" s="4" t="s">
         <v>825</v>
       </c>
@@ -11048,7 +10778,6 @@
       <c r="C223" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="D223" s="1"/>
       <c r="E223" s="1" t="s">
         <v>894</v>
       </c>
@@ -11058,7 +10787,6 @@
       <c r="G223" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H223" s="1"/>
       <c r="J223" s="4" t="s">
         <v>832</v>
       </c>
@@ -11073,14 +10801,12 @@
       <c r="C224" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="D224" s="1"/>
       <c r="E224" s="1">
         <v>1885</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="G224" s="1"/>
       <c r="H224" s="1" t="s">
         <v>262</v>
       </c>
@@ -11098,15 +10824,12 @@
       <c r="C225" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="D225" s="1"/>
       <c r="E225" s="1" t="s">
         <v>902</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="G225" s="1"/>
-      <c r="H225" s="1"/>
       <c r="J225" s="4" t="s">
         <v>903</v>
       </c>
@@ -11121,7 +10844,6 @@
       <c r="C226" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D226" s="1"/>
       <c r="E226" s="1" t="s">
         <v>902</v>
       </c>
@@ -11131,7 +10853,6 @@
       <c r="G226" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H226" s="1"/>
       <c r="J226" s="4" t="s">
         <v>905</v>
       </c>
@@ -11143,16 +10864,12 @@
       <c r="B227" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
       <c r="E227" s="1">
         <v>1887</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="G227" s="1"/>
-      <c r="H227" s="1"/>
       <c r="J227" s="4" t="s">
         <v>825</v>
       </c>
@@ -11173,7 +10890,6 @@
       <c r="F228" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="G228" s="1"/>
       <c r="H228" s="1" t="s">
         <v>631</v>
       </c>
@@ -11197,7 +10913,6 @@
       <c r="F229" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="G229" s="1"/>
       <c r="J229" s="4" t="s">
         <v>914</v>
       </c>
@@ -11244,7 +10959,6 @@
       <c r="G231" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H231" s="1"/>
       <c r="J231" s="4" t="s">
         <v>918</v>
       </c>
@@ -11305,7 +11019,6 @@
       <c r="B234" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="C234" s="1"/>
       <c r="D234" s="1" t="s">
         <v>932</v>
       </c>
@@ -11361,7 +11074,6 @@
       <c r="F236" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="G236" s="1"/>
       <c r="H236" s="1" t="s">
         <v>175</v>
       </c>
@@ -11379,14 +11091,12 @@
       <c r="C237" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="D237" s="1"/>
       <c r="E237" s="1" t="s">
         <v>943</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="G237" s="1"/>
       <c r="H237" s="1" t="s">
         <v>262</v>
       </c>
@@ -11459,7 +11169,6 @@
       <c r="F240" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="G240" s="1"/>
       <c r="H240" s="1" t="s">
         <v>243</v>
       </c>
@@ -11506,11 +11215,9 @@
       <c r="F242" s="2" t="s">
         <v>957</v>
       </c>
-      <c r="G242" s="1"/>
       <c r="H242" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I242" s="3"/>
       <c r="J242" s="4" t="s">
         <v>825</v>
       </c>
@@ -11531,8 +11238,6 @@
       <c r="F243" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="G243" s="1"/>
-      <c r="H243" s="1"/>
       <c r="J243" s="4" t="s">
         <v>961</v>
       </c>
@@ -11544,7 +11249,6 @@
       <c r="B244" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="C244" s="1"/>
       <c r="E244" s="1">
         <v>1893</v>
       </c>
@@ -11554,7 +11258,6 @@
       <c r="G244" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H244" s="1"/>
       <c r="J244" s="4" t="s">
         <v>832</v>
       </c>
@@ -11578,7 +11281,6 @@
       <c r="G245" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H245" s="1"/>
       <c r="J245" s="4" t="s">
         <v>832</v>
       </c>
@@ -11590,8 +11292,6 @@
       <c r="B246" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="C246" s="1"/>
-      <c r="D246" s="1"/>
       <c r="E246" s="1">
         <v>1893</v>
       </c>
@@ -11601,7 +11301,6 @@
       <c r="G246" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H246" s="1"/>
       <c r="J246" s="4" t="s">
         <v>832</v>
       </c>
@@ -11636,8 +11335,6 @@
       <c r="B248" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="C248" s="1"/>
-      <c r="D248" s="1"/>
       <c r="E248" s="1">
         <v>1893</v>
       </c>
@@ -11658,7 +11355,6 @@
       <c r="C249" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="D249" s="1"/>
       <c r="E249" s="1">
         <v>1893</v>
       </c>
@@ -11668,7 +11364,6 @@
       <c r="H249" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I249" s="3"/>
       <c r="J249" s="4" t="s">
         <v>825</v>
       </c>
@@ -11700,8 +11395,6 @@
       <c r="B251" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="C251" s="1"/>
-      <c r="D251" s="1"/>
       <c r="E251" s="1">
         <v>1893</v>
       </c>
@@ -11742,7 +11435,6 @@
       <c r="B253" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="C253" s="1"/>
       <c r="E253" s="1" t="s">
         <v>986</v>
       </c>
@@ -11763,7 +11455,6 @@
       <c r="C254" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="D254" s="1"/>
       <c r="E254" s="1">
         <v>1867</v>
       </c>
@@ -11784,15 +11475,12 @@
       <c r="C255" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="D255" s="1"/>
       <c r="E255" s="1">
         <v>1871</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="G255" s="1"/>
-      <c r="H255" s="1"/>
       <c r="J255" s="4" t="s">
         <v>998</v>
       </c>
@@ -11813,8 +11501,6 @@
       <c r="F256" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="G256" s="1"/>
-      <c r="H256" s="1"/>
       <c r="J256" s="4" t="s">
         <v>1002</v>
       </c>
@@ -11829,7 +11515,6 @@
       <c r="C257" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="D257" s="1"/>
       <c r="E257" s="1">
         <v>1868</v>
       </c>
@@ -11839,7 +11524,6 @@
       <c r="G257" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H257" s="1"/>
       <c r="J257" s="4" t="s">
         <v>1007</v>
       </c>
@@ -11863,7 +11547,6 @@
       <c r="G258" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H258" s="1"/>
       <c r="J258" s="4" t="s">
         <v>1007</v>
       </c>
@@ -11878,7 +11561,6 @@
       <c r="C259" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="D259" s="1"/>
       <c r="E259" s="1">
         <v>1871</v>
       </c>
@@ -11888,7 +11570,6 @@
       <c r="G259" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H259" s="1"/>
       <c r="J259" s="4" t="s">
         <v>1007</v>
       </c>
@@ -11903,7 +11584,6 @@
       <c r="C260" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="D260" s="1"/>
       <c r="E260" s="1">
         <v>1871</v>
       </c>
@@ -11913,7 +11593,6 @@
       <c r="G260" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H260" s="1"/>
       <c r="J260" s="4" t="s">
         <v>1007</v>
       </c>
@@ -11928,7 +11607,6 @@
       <c r="C261" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="D261" s="1"/>
       <c r="E261" s="1">
         <v>1871</v>
       </c>
@@ -11938,7 +11616,6 @@
       <c r="G261" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H261" s="1"/>
       <c r="J261" s="4" t="s">
         <v>1007</v>
       </c>
@@ -11953,7 +11630,6 @@
       <c r="C262" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="D262" s="1"/>
       <c r="E262" s="1">
         <v>1871</v>
       </c>
@@ -11963,7 +11639,6 @@
       <c r="G262" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H262" s="1"/>
       <c r="J262" s="4" t="s">
         <v>1007</v>
       </c>
@@ -11987,7 +11662,6 @@
       <c r="G263" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H263" s="1"/>
       <c r="J263" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12002,7 +11676,6 @@
       <c r="C264" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="D264" s="1"/>
       <c r="E264" s="1">
         <v>1872</v>
       </c>
@@ -12012,8 +11685,6 @@
       <c r="G264" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H264" s="1"/>
-      <c r="I264" s="3"/>
       <c r="J264" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12028,7 +11699,6 @@
       <c r="C265" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="D265" s="1"/>
       <c r="E265" s="1">
         <v>1872</v>
       </c>
@@ -12038,8 +11708,6 @@
       <c r="G265" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H265" s="1"/>
-      <c r="I265" s="3"/>
       <c r="J265" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12054,7 +11722,6 @@
       <c r="C266" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="D266" s="1"/>
       <c r="E266" s="1">
         <v>1872</v>
       </c>
@@ -12064,8 +11731,6 @@
       <c r="G266" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H266" s="1"/>
-      <c r="I266" s="3"/>
       <c r="J266" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12080,7 +11745,6 @@
       <c r="C267" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="D267" s="1"/>
       <c r="E267" s="1">
         <v>1872</v>
       </c>
@@ -12090,8 +11754,6 @@
       <c r="G267" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H267" s="1"/>
-      <c r="I267" s="3"/>
       <c r="J267" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12115,7 +11777,6 @@
       <c r="G268" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H268" s="1"/>
       <c r="J268" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12130,7 +11791,6 @@
       <c r="C269" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="D269" s="1"/>
       <c r="E269" s="1">
         <v>1872</v>
       </c>
@@ -12140,7 +11800,6 @@
       <c r="G269" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H269" s="1"/>
       <c r="J269" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12155,7 +11814,6 @@
       <c r="C270" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="D270" s="1"/>
       <c r="E270" s="1">
         <v>1872</v>
       </c>
@@ -12179,7 +11837,6 @@
       <c r="C271" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="D271" s="1"/>
       <c r="E271" s="1">
         <v>1872</v>
       </c>
@@ -12189,8 +11846,6 @@
       <c r="G271" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H271" s="1"/>
-      <c r="I271" s="3"/>
       <c r="J271" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12205,7 +11860,6 @@
       <c r="C272" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="D272" s="1"/>
       <c r="E272" s="1">
         <v>1872</v>
       </c>
@@ -12215,8 +11869,6 @@
       <c r="G272" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H272" s="1"/>
-      <c r="I272" s="3"/>
       <c r="J272" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12231,7 +11883,6 @@
       <c r="C273" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="D273" s="1"/>
       <c r="E273" s="1">
         <v>1873</v>
       </c>
@@ -12241,7 +11892,6 @@
       <c r="G273" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H273" s="1"/>
       <c r="J273" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12256,7 +11906,6 @@
       <c r="C274" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="D274" s="1"/>
       <c r="E274" s="1">
         <v>1873</v>
       </c>
@@ -12266,8 +11915,6 @@
       <c r="G274" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H274" s="1"/>
-      <c r="I274" s="3"/>
       <c r="J274" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12282,16 +11929,12 @@
       <c r="C275" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="D275" s="1"/>
       <c r="E275" s="1">
         <v>1873</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="G275" s="1"/>
-      <c r="H275" s="1"/>
-      <c r="I275" s="3"/>
       <c r="J275" s="4" t="s">
         <v>1063</v>
       </c>
@@ -12306,7 +11949,6 @@
       <c r="C276" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="D276" s="1"/>
       <c r="E276" s="1">
         <v>1873</v>
       </c>
@@ -12316,8 +11958,6 @@
       <c r="G276" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H276" s="1"/>
-      <c r="I276" s="3"/>
       <c r="J276" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12332,7 +11972,6 @@
       <c r="C277" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="D277" s="1"/>
       <c r="E277" s="1">
         <v>1873</v>
       </c>
@@ -12342,8 +11981,6 @@
       <c r="G277" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H277" s="1"/>
-      <c r="I277" s="3"/>
       <c r="J277" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12358,7 +11995,6 @@
       <c r="C278" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="D278" s="1"/>
       <c r="E278" s="1">
         <v>1873</v>
       </c>
@@ -12368,8 +12004,6 @@
       <c r="G278" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H278" s="1"/>
-      <c r="I278" s="3"/>
       <c r="J278" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12384,7 +12018,6 @@
       <c r="C279" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="D279" s="1"/>
       <c r="E279" s="1">
         <v>1873</v>
       </c>
@@ -12394,8 +12027,6 @@
       <c r="G279" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H279" s="1"/>
-      <c r="I279" s="3"/>
       <c r="J279" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12465,7 +12096,6 @@
       <c r="G282" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H282" s="1"/>
       <c r="J282" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12489,7 +12119,6 @@
       <c r="G283" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H283" s="1"/>
       <c r="J283" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12504,7 +12133,6 @@
       <c r="C284" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="D284" s="1"/>
       <c r="E284" s="1">
         <v>1874</v>
       </c>
@@ -12560,7 +12188,6 @@
       <c r="G286" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H286" s="1"/>
       <c r="J286" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12598,7 +12225,6 @@
       <c r="C288" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="D288" s="1"/>
       <c r="E288" s="1">
         <v>1874</v>
       </c>
@@ -12622,7 +12248,6 @@
       <c r="C289" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="D289" s="1"/>
       <c r="E289" s="1">
         <v>1874</v>
       </c>
@@ -12646,7 +12271,6 @@
       <c r="C290" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="D290" s="1"/>
       <c r="E290" s="1">
         <v>1874</v>
       </c>
@@ -12656,7 +12280,6 @@
       <c r="G290" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H290" s="1"/>
       <c r="J290" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12671,7 +12294,6 @@
       <c r="C291" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="D291" s="1"/>
       <c r="E291" s="1">
         <v>1874</v>
       </c>
@@ -12681,7 +12303,6 @@
       <c r="G291" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H291" s="1"/>
       <c r="J291" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12696,7 +12317,6 @@
       <c r="C292" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="D292" s="1"/>
       <c r="E292" s="1">
         <v>1874</v>
       </c>
@@ -12706,7 +12326,6 @@
       <c r="G292" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H292" s="1"/>
       <c r="J292" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12721,7 +12340,6 @@
       <c r="C293" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="D293" s="1"/>
       <c r="E293" s="1">
         <v>1874</v>
       </c>
@@ -12731,7 +12349,6 @@
       <c r="G293" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H293" s="1"/>
       <c r="J293" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12746,7 +12363,6 @@
       <c r="C294" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="D294" s="1"/>
       <c r="E294" s="1">
         <v>1874</v>
       </c>
@@ -12756,7 +12372,6 @@
       <c r="G294" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H294" s="1"/>
       <c r="J294" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12771,7 +12386,6 @@
       <c r="C295" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="D295" s="1"/>
       <c r="E295" s="1">
         <v>1874</v>
       </c>
@@ -12795,7 +12409,6 @@
       <c r="C296" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="D296" s="1"/>
       <c r="E296" s="1">
         <v>1874</v>
       </c>
@@ -12805,7 +12418,6 @@
       <c r="G296" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H296" s="1"/>
       <c r="J296" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12820,7 +12432,6 @@
       <c r="C297" s="1" t="s">
         <v>1125</v>
       </c>
-      <c r="D297" s="1"/>
       <c r="E297" s="1">
         <v>1874</v>
       </c>
@@ -12844,7 +12455,6 @@
       <c r="C298" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="D298" s="1"/>
       <c r="E298" s="1">
         <v>1874</v>
       </c>
@@ -12868,7 +12478,6 @@
       <c r="C299" s="1" t="s">
         <v>1131</v>
       </c>
-      <c r="D299" s="1"/>
       <c r="E299" s="1" t="s">
         <v>266</v>
       </c>
@@ -12892,7 +12501,6 @@
       <c r="C300" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="D300" s="1"/>
       <c r="E300" s="1">
         <v>1875</v>
       </c>
@@ -12916,7 +12524,6 @@
       <c r="C301" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="D301" s="1"/>
       <c r="E301" s="1">
         <v>1875</v>
       </c>
@@ -12926,7 +12533,6 @@
       <c r="G301" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H301" s="1"/>
       <c r="J301" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12941,7 +12547,6 @@
       <c r="C302" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="D302" s="1"/>
       <c r="E302" s="1">
         <v>1875</v>
       </c>
@@ -12965,7 +12570,6 @@
       <c r="C303" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="D303" s="1"/>
       <c r="E303" s="1">
         <v>1875</v>
       </c>
@@ -12975,7 +12579,6 @@
       <c r="G303" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H303" s="1"/>
       <c r="J303" s="4" t="s">
         <v>1026</v>
       </c>
@@ -12990,7 +12593,6 @@
       <c r="C304" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="D304" s="1"/>
       <c r="E304" s="1">
         <v>1875</v>
       </c>
@@ -13014,7 +12616,6 @@
       <c r="C305" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="D305" s="1"/>
       <c r="E305" s="1">
         <v>1875</v>
       </c>
@@ -13038,7 +12639,6 @@
       <c r="C306" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="D306" s="1"/>
       <c r="E306" s="1">
         <v>1875</v>
       </c>
@@ -13048,7 +12648,6 @@
       <c r="G306" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H306" s="1"/>
       <c r="J306" s="4" t="s">
         <v>1026</v>
       </c>
@@ -13141,7 +12740,6 @@
       <c r="G310" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H310" s="1"/>
       <c r="J310" s="4" t="s">
         <v>1026</v>
       </c>
@@ -13211,7 +12809,6 @@
       <c r="G313" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="H313" s="1"/>
       <c r="J313" s="4" t="s">
         <v>1026</v>
       </c>
@@ -13272,15 +12869,12 @@
       <c r="C316" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="D316" s="1"/>
       <c r="E316" s="1">
         <v>1888</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="G316" s="1"/>
-      <c r="H316" s="1"/>
       <c r="J316" s="4" t="s">
         <v>1185</v>
       </c>
@@ -13324,8 +12918,6 @@
       <c r="F318" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="G318" s="1"/>
-      <c r="H318" s="1"/>
       <c r="J318" s="4" t="s">
         <v>1193</v>
       </c>
@@ -13363,14 +12955,12 @@
       <c r="C320" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="D320" s="1"/>
       <c r="E320" s="1">
         <v>1892</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="G320" s="1"/>
       <c r="J320" s="4" t="s">
         <v>1006</v>
       </c>
@@ -13391,7 +12981,6 @@
       <c r="F321" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="G321" s="1"/>
       <c r="J321" s="4" t="s">
         <v>1205</v>
       </c>
@@ -13403,8 +12992,6 @@
       <c r="B322" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="C322" s="1"/>
-      <c r="D322" s="1"/>
       <c r="E322" s="4">
         <v>1891</v>
       </c>
@@ -13414,7 +13001,6 @@
       <c r="G322" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="H322" s="1"/>
       <c r="J322" s="2" t="s">
         <v>1209</v>
       </c>
@@ -13438,7 +13024,6 @@
       <c r="G323" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="H323" s="1"/>
       <c r="J323" s="2" t="s">
         <v>1213</v>
       </c>
@@ -13453,7 +13038,6 @@
       <c r="C324" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="D324" s="1"/>
       <c r="E324" s="4">
         <v>1892</v>
       </c>
@@ -13463,8 +13047,6 @@
       <c r="G324" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="H324" s="1"/>
-      <c r="I324" s="3"/>
       <c r="J324" s="2" t="s">
         <v>1217</v>
       </c>
@@ -13479,7 +13061,6 @@
       <c r="C325" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="D325" s="1"/>
       <c r="E325" s="4">
         <v>1892</v>
       </c>
@@ -13500,7 +13081,6 @@
       <c r="B326" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="C326" s="1"/>
       <c r="E326" s="4">
         <v>1893</v>
       </c>
@@ -13521,7 +13101,6 @@
       <c r="B327" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="C327" s="1"/>
       <c r="E327" s="4">
         <v>1893</v>
       </c>
@@ -13542,8 +13121,6 @@
       <c r="B328" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="C328" s="1"/>
-      <c r="D328" s="1"/>
       <c r="E328" s="4">
         <v>1893</v>
       </c>
@@ -13553,7 +13130,6 @@
       <c r="G328" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="H328" s="1"/>
       <c r="J328" s="2" t="s">
         <v>1223</v>
       </c>
@@ -13568,7 +13144,6 @@
       <c r="C329" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="D329" s="1"/>
       <c r="E329" s="1">
         <v>1865</v>
       </c>
@@ -13578,8 +13153,6 @@
       <c r="G329" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="H329" s="1"/>
-      <c r="I329" s="3"/>
       <c r="J329" s="4" t="s">
         <v>1233</v>
       </c>
@@ -13603,7 +13176,6 @@
       <c r="G330" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="H330" s="1"/>
       <c r="J330" s="4" t="s">
         <v>1237</v>
       </c>
@@ -13627,7 +13199,6 @@
       <c r="G331" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="H331" s="1"/>
       <c r="J331" s="4" t="s">
         <v>1241</v>
       </c>
@@ -13743,7 +13314,6 @@
       <c r="G336" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="H336" s="1"/>
       <c r="J336" s="4" t="s">
         <v>1262</v>
       </c>
@@ -13764,7 +13334,6 @@
       <c r="F337" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="G337" s="1"/>
       <c r="J337" s="4" t="s">
         <v>1266</v>
       </c>
@@ -13776,8 +13345,6 @@
       <c r="B338" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="C338" s="1"/>
-      <c r="D338" s="1"/>
       <c r="E338" s="4">
         <v>1844</v>
       </c>
@@ -13901,7 +13468,6 @@
       <c r="C344" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D344" s="1"/>
       <c r="E344" s="4">
         <v>1847</v>
       </c>
@@ -13962,7 +13528,6 @@
       <c r="C347" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D347" s="1"/>
       <c r="E347" s="4">
         <v>1848</v>
       </c>
@@ -13983,7 +13548,6 @@
       <c r="C348" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D348" s="1"/>
       <c r="E348" s="4">
         <v>1848</v>
       </c>
@@ -14004,7 +13568,6 @@
       <c r="C349" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D349" s="1"/>
       <c r="E349" s="4">
         <v>1848</v>
       </c>
@@ -14045,7 +13608,6 @@
       <c r="C351" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D351" s="1"/>
       <c r="E351" s="4">
         <v>1848</v>
       </c>
@@ -14126,7 +13688,6 @@
       <c r="C355" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D355" s="1"/>
       <c r="E355" s="4">
         <v>1848</v>
       </c>
@@ -14147,7 +13708,6 @@
       <c r="C356" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D356" s="1"/>
       <c r="E356" s="4">
         <v>1848</v>
       </c>
@@ -14168,7 +13728,6 @@
       <c r="C357" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D357" s="1"/>
       <c r="E357" s="4">
         <v>1848</v>
       </c>
@@ -14229,7 +13788,6 @@
       <c r="C360" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D360" s="1"/>
       <c r="E360" s="4">
         <v>1848</v>
       </c>
@@ -14250,7 +13808,6 @@
       <c r="C361" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D361" s="1"/>
       <c r="E361" s="4">
         <v>1848</v>
       </c>
@@ -14271,7 +13828,6 @@
       <c r="C362" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D362" s="1"/>
       <c r="E362" s="4">
         <v>1848</v>
       </c>
@@ -14289,7 +13845,6 @@
       <c r="B363" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="C363" s="1"/>
       <c r="E363" s="4">
         <v>1854</v>
       </c>
@@ -14307,7 +13862,6 @@
       <c r="B364" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="C364" s="1"/>
       <c r="E364" s="4">
         <v>1855</v>
       </c>
@@ -14328,7 +13882,6 @@
       <c r="C365" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="D365" s="1"/>
       <c r="E365" s="4">
         <v>1861</v>
       </c>
@@ -14349,7 +13902,6 @@
       <c r="C366" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="D366" s="1"/>
       <c r="E366" s="4">
         <v>1865</v>
       </c>
@@ -14390,7 +13942,6 @@
       <c r="C368" s="1" t="s">
         <v>1339</v>
       </c>
-      <c r="D368" s="1"/>
       <c r="E368" s="4" t="s">
         <v>1336</v>
       </c>
@@ -14411,7 +13962,6 @@
       <c r="C369" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="D369" s="1"/>
       <c r="E369" s="4" t="s">
         <v>1336</v>
       </c>
@@ -14452,7 +14002,6 @@
       <c r="C371" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="D371" s="1"/>
       <c r="E371" s="4" t="s">
         <v>1336</v>
       </c>
@@ -14473,7 +14022,6 @@
       <c r="C372" s="1" t="s">
         <v>1351</v>
       </c>
-      <c r="D372" s="1"/>
       <c r="E372" s="4" t="s">
         <v>1336</v>
       </c>
@@ -14494,7 +14042,6 @@
       <c r="C373" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="D373" s="1"/>
       <c r="E373" s="4">
         <v>1871</v>
       </c>
@@ -14515,7 +14062,6 @@
       <c r="C374" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="D374" s="1"/>
       <c r="E374" s="4">
         <v>1872</v>
       </c>
@@ -14536,7 +14082,6 @@
       <c r="C375" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="D375" s="1"/>
       <c r="E375" s="4">
         <v>1872</v>
       </c>
@@ -14577,7 +14122,6 @@
       <c r="C377" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="D377" s="1"/>
       <c r="E377" s="4">
         <v>1876</v>
       </c>
@@ -14598,7 +14142,6 @@
       <c r="C378" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="D378" s="1"/>
       <c r="E378" s="4">
         <v>1876</v>
       </c>
@@ -14616,8 +14159,6 @@
       <c r="B379" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="C379" s="1"/>
-      <c r="D379" s="1"/>
       <c r="E379" s="4">
         <v>1877</v>
       </c>
@@ -14638,7 +14179,6 @@
       <c r="C380" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="D380" s="1"/>
       <c r="E380" s="4">
         <v>1878</v>
       </c>
@@ -14659,7 +14199,6 @@
       <c r="C381" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="D381" s="1"/>
       <c r="E381" s="4">
         <v>1880</v>
       </c>
@@ -14680,7 +14219,6 @@
       <c r="C382" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="D382" s="1"/>
       <c r="E382" s="4">
         <v>1880</v>
       </c>
@@ -14698,8 +14236,6 @@
       <c r="B383" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="C383" s="1"/>
-      <c r="D383" s="1"/>
       <c r="E383" s="4">
         <v>1882</v>
       </c>
@@ -14760,7 +14296,6 @@
       <c r="C386" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="D386" s="1"/>
       <c r="E386" s="4" t="s">
         <v>1392</v>
       </c>
@@ -14795,7 +14330,6 @@
       <c r="C388" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="D388" s="1"/>
       <c r="E388" s="4">
         <v>1892</v>
       </c>
@@ -14805,8 +14339,6 @@
       <c r="G388" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="H388" s="1"/>
-      <c r="I388" s="3"/>
       <c r="J388" s="2" t="s">
         <v>1399</v>
       </c>
@@ -14821,7 +14353,6 @@
       <c r="F389" s="2" t="s">
         <v>1401</v>
       </c>
-      <c r="G389" s="1"/>
       <c r="J389" s="4" t="s">
         <v>1402</v>
       </c>
@@ -14836,8 +14367,6 @@
       <c r="F390" s="2" t="s">
         <v>1404</v>
       </c>
-      <c r="G390" s="1"/>
-      <c r="H390" s="1"/>
       <c r="J390" s="4" t="s">
         <v>1405</v>
       </c>
@@ -14852,7 +14381,6 @@
       <c r="F391" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="G391" s="1"/>
       <c r="J391" s="4" t="s">
         <v>1405</v>
       </c>
@@ -14878,7 +14406,6 @@
       <c r="C393" s="1" t="s">
         <v>1411</v>
       </c>
-      <c r="D393" s="1"/>
       <c r="E393" s="1">
         <v>1884</v>
       </c>
@@ -14888,7 +14415,6 @@
       <c r="G393" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H393" s="1"/>
       <c r="J393" s="4" t="s">
         <v>832</v>
       </c>
@@ -14897,7 +14423,6 @@
       <c r="C394" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="D394" s="1"/>
       <c r="E394" s="1">
         <v>1878</v>
       </c>
@@ -14907,7 +14432,6 @@
       <c r="G394" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H394" s="1"/>
       <c r="J394" s="4" t="s">
         <v>1415</v>
       </c>
@@ -14925,7 +14449,6 @@
       <c r="G395" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H395" s="1"/>
       <c r="J395" s="4" t="s">
         <v>1418</v>
       </c>
@@ -14940,7 +14463,6 @@
       <c r="F396" s="2" t="s">
         <v>1421</v>
       </c>
-      <c r="G396" s="1"/>
       <c r="J396" s="4" t="s">
         <v>546</v>
       </c>
@@ -14955,7 +14477,6 @@
       <c r="F397" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="G397" s="1"/>
       <c r="J397" s="4" t="s">
         <v>1424</v>
       </c>
@@ -14964,14 +14485,12 @@
       <c r="C398" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="D398" s="1"/>
       <c r="E398" s="1" t="s">
         <v>1426</v>
       </c>
       <c r="F398" s="2" t="s">
         <v>1427</v>
       </c>
-      <c r="G398" s="1"/>
       <c r="J398" s="4" t="s">
         <v>1428</v>
       </c>
@@ -15034,7 +14553,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J402" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:J402">
+    <sortState ref="A1:J402">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
